--- a/assets/templates/mof_r6.xlsx
+++ b/assets/templates/mof_r6.xlsx
@@ -609,7 +609,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -724,6 +724,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1449,6 +1461,7 @@
       <c r="B6" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="C6" s="66"/>
       <c r="I6" t="s">
         <v>10</v>
       </c>
@@ -1484,17 +1497,17 @@
       <c r="B9" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="26"/>
+      <c r="D9" s="63"/>
       <c r="E9" s="26"/>
       <c r="F9" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="26"/>
+      <c r="G9" s="63"/>
       <c r="H9" s="26"/>
       <c r="I9" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="26"/>
+      <c r="J9" s="63"/>
       <c r="K9" s="26"/>
       <c r="L9" s="1"/>
     </row>
@@ -1580,17 +1593,17 @@
         <v>29</v>
       </c>
       <c r="C17" s="45"/>
-      <c r="D17" s="26"/>
+      <c r="D17" s="63"/>
       <c r="E17" s="26"/>
       <c r="F17" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="63"/>
       <c r="H17" s="26"/>
       <c r="I17" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="26"/>
+      <c r="J17" s="63"/>
       <c r="K17" s="26"/>
       <c r="L17" s="1"/>
     </row>
@@ -1599,12 +1612,12 @@
         <v>32</v>
       </c>
       <c r="C18" s="45"/>
-      <c r="D18" s="26"/>
+      <c r="D18" s="63"/>
       <c r="E18" s="26"/>
       <c r="F18" t="s">
         <v>33</v>
       </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="63"/>
       <c r="H18" s="26"/>
       <c r="L18" s="1"/>
     </row>
@@ -1616,20 +1629,20 @@
         <v>34</v>
       </c>
       <c r="C19" s="45"/>
-      <c r="D19" s="26"/>
+      <c r="D19" s="63"/>
       <c r="E19" s="26"/>
       <c r="F19" t="s">
         <v>35</v>
       </c>
-      <c r="G19" s="22"/>
+      <c r="G19" s="64"/>
       <c r="H19" t="s">
         <v>36</v>
       </c>
-      <c r="I19" s="22"/>
+      <c r="I19" s="64"/>
       <c r="J19" t="s">
         <v>36</v>
       </c>
-      <c r="K19" s="26"/>
+      <c r="K19" s="63"/>
       <c r="L19" s="27"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
@@ -1637,18 +1650,18 @@
       <c r="B20" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D20" s="26"/>
+      <c r="D20" s="63"/>
       <c r="E20" s="26"/>
       <c r="F20" t="s">
         <v>38</v>
       </c>
-      <c r="G20" s="22"/>
+      <c r="G20" s="64"/>
       <c r="H20" s="22"/>
       <c r="I20" s="22"/>
       <c r="J20" t="s">
         <v>39</v>
       </c>
-      <c r="K20" s="26"/>
+      <c r="K20" s="63"/>
       <c r="L20" s="27"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
@@ -1657,7 +1670,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="45"/>
-      <c r="D21" s="28"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="28"/>
       <c r="F21" s="28"/>
       <c r="L21" s="1"/>
